--- a/registration_forms/034_experiment_participant_information_collection_form--registration_forms.xlsx
+++ b/registration_forms/034_experiment_participant_information_collection_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -528,10 +528,14 @@
           <t>Experiment Participant Information</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Brief description of the experiment participant.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +552,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>participant_name</t>
+          <t>Participant Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,12 +570,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>experiment_participant_information_collection_form</t>
+          <t>participant_phone_number</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>experiment participant information collection form</t>
+          <t>Participant Phone Number</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,35 +593,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>participant_phone_number</t>
+          <t>participant_email</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>participant phone number</t>
+          <t>Participant Email</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>participant_email</t>
+          <t>participant_dob</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>participant email</t>
+          <t>Participant Date of Birth</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,40 +634,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>participant_address</t>
+          <t>participant_education_level</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>participant address</t>
+          <t>Participant Education Level</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>participant_dob</t>
+          <t>participant_education_fields</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>participant date of birth</t>
+          <t>Participant Education Fields</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,20 +680,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>participant_education_level</t>
+          <t>participant_languages_spoken</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>participant education level</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Participant Languages Spoken</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>List of languages spoken by the participant.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -699,17 +707,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>participant_education_fields</t>
+          <t>participant_languages_spoken_other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>participant education fields</t>
+          <t>Participant Languages Spoken Other</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +735,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>participant_education_institutions</t>
+          <t>participant_languages_spoken_count</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>participant education institutions</t>
+          <t>Participant Languages Spoken Count</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +758,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>participant_hobbies</t>
+          <t>participant_education_institutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>participant hobbies</t>
+          <t>Participant Education Institutions</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +781,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>participant_languages_spoken</t>
+          <t>participant_hobbies</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>participant languages spoken</t>
+          <t>Participant Hobbies</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +804,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>participant_languages_spoken_other</t>
+          <t>participant_languages_spoken_other_languages</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>participant languages spoken other</t>
+          <t>Participant Languages Spoken Other Languages</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,729 +827,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>participant_languages_spoken_other_languages</t>
+          <t>participant_languages_spoken_count_other_languages</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>participant languages spoken other languages</t>
+          <t>Participant Languages Spoken Count Other Languages</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>participant_languages_spoken_count</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>participant languages spoken count</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>participant_languages_spoken_other_languages_count</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>participant languages spoken other languages count</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>participant_languages_spoken_languages_other_languages</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>participant languages spoken other languages other languages</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>participant_languages_spoken_count_other_languages</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>participant languages spoken other languages count</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>participant_languages_spoken_languages_count</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>participant languages spoken languages count</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>participant_languages_spoken_count_languages</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>participant languages spoken languages count languages</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>participant_languages_spoken_other_languages_count_languages</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>participant languages spoken other languages count languages</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>participant_languages_spoken_languages_count_languages_count</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>participant languages spoken languages count languages count</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>participant_languages_spoken_count_languages_spoken</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>participant languages spoken languages spoken</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>participant_languages_spoken_count_languages</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>participant languages spoken languages</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>participant_languages_spoken_count</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>participant languages spoken count</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>participant_languages_spoken</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>participant languages spoken</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>participant_languages_spoken_count_other_languages_count</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>participant languages spoken other languages count count</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>participant_languages_spoken_count_languages_count_count</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>participant languages spoken languages count languages count count</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>participant_languages_spoken_count_languages</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>participant languages spoken languages</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>participant_languages_spoken_count_other</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>participant languages spoken other</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>participant_languages_spoken_other_count</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>participant languages spoken other count</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>participant_languages_spoken</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>participant languages spoken</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>participant_languages_spoken_count_other_count</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>participant languages spoken other count count count</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>participant_languages_spoken_count_count</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>participant languages spoken languages count count count</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>participant_languages_spoken_count_count</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>participant languages spoken count count</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>participant_languages_spoken_count_other</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>participant languages spoken other</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>participant_languages_spoken_count</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>participant languages spoken count</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>participant_languages_spoken_count_languages_count</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>participant languages spoken count languages count</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>participant_languages_spoken_other_count_count</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>participant languages spoken other count count</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>participant_languages_spoken_count_count_count</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>participant languages spoken languages count count count</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>participant_languages_spoken_count</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>participant languages spoken count</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>participant_languages_spoken_other_count_count</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>participant languages spoken other count count</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>participant_languages_spoken_count_count_other</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>participant languages spoken count count other</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>participant_languages_spoken_count_count_count_other</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>participant languages spoken count count count other</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>participant_languages_spoken_count_count</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>participant languages spoken count count count</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1558,12 +853,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1591,12 +886,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High School'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -1608,12 +903,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'bachelor'}</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Bachelor'}</t>
+          <t>Bachelor</t>
         </is>
       </c>
     </row>
@@ -1625,12 +920,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'masters'}</t>
+          <t>masters</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Masters'}</t>
+          <t>Masters</t>
         </is>
       </c>
     </row>
@@ -1642,29 +937,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'doctoral'}</t>
+          <t>doctoral</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Doctoral'}</t>
+          <t>Doctoral</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>participant_education_level_choices</t>
+          <t>participant_education_fields_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other'}</t>
+          <t>arts</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
+          <t>Arts</t>
         </is>
       </c>
     </row>
@@ -1676,12 +971,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'arts'}</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Arts'}</t>
+          <t>Engineering</t>
         </is>
       </c>
     </row>
@@ -1693,12 +988,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'engineering'}</t>
+          <t>medicine</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Engineering'}</t>
+          <t>Medicine</t>
         </is>
       </c>
     </row>
@@ -1710,46 +1005,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'medicine'}</t>
+          <t>science</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Medicine'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>participant_education_fields_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'id':_4,_'label':_'science'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'id': 4, 'label': 'Science'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>participant_education_fields_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>{'id':_5,_'label':_'other'}</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
+          <t>Science</t>
         </is>
       </c>
     </row>
